--- a/InputData/indst/CSoIO/Cement Share of Industry 239 Output.xlsx
+++ b/InputData/indst/CSoIO/Cement Share of Industry 239 Output.xlsx
@@ -642,9 +642,10 @@
         <f>ROUND(B4/B5,3)</f>
         <v/>
       </c>
-      <c r="C6">
-        <f> 0.154 (was 0.21 on the external-BEA basis - corrected 2026-08-27)</f>
-        <v/>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>0.154 (was 0.21 on the external-BEA basis - corrected 2026-08-27)</t>
+        </is>
       </c>
     </row>
   </sheetData>
